--- a/main/ig/ValueSet-fr-additional-when-codes.xlsx
+++ b/main/ig/ValueSet-fr-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-05T08:58:38+00:00</t>
+    <t>2025-11-07T10:40:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-additional-when-codes.xlsx
+++ b/main/ig/ValueSet-fr-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-07T10:40:44+00:00</t>
+    <t>2025-11-25T08:22:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-additional-when-codes.xlsx
+++ b/main/ig/ValueSet-fr-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T08:22:04+00:00</t>
+    <t>2026-01-16T18:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-additional-when-codes.xlsx
+++ b/main/ig/ValueSet-fr-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T18:04:25+00:00</t>
+    <t>2026-01-23T16:54:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-additional-when-codes.xlsx
+++ b/main/ig/ValueSet-fr-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T16:54:57+00:00</t>
+    <t>2026-01-23T16:56:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-additional-when-codes.xlsx
+++ b/main/ig/ValueSet-fr-additional-when-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T16:56:48+00:00</t>
+    <t>2026-02-09T09:37:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
